--- a/LCA_techV3.xlsx
+++ b/LCA_techV3.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Users\hravoaha\Desktop\Thèse\Thèse 2023\Objectif 2\biowaste_optim\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C623DDF7-3023-435F-A3B3-2BE0A6621C62}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E88FB3CC-E10D-4048-9F87-F50E1EC2C8D6}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="19200" windowHeight="6640" xr2:uid="{D3821372-1969-4DD6-A628-04C5F8F02CF2}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="19200" windowHeight="6640" activeTab="11" xr2:uid="{D3821372-1969-4DD6-A628-04C5F8F02CF2}"/>
   </bookViews>
   <sheets>
     <sheet name="LCIA_AD-f" sheetId="38" r:id="rId1"/>
@@ -2403,8 +2403,8 @@
       <sheetName val="Variables"/>
     </sheetNames>
     <sheetDataSet>
-      <sheetData sheetId="0"/>
-      <sheetData sheetId="1"/>
+      <sheetData sheetId="0" refreshError="1"/>
+      <sheetData sheetId="1" refreshError="1"/>
       <sheetData sheetId="2">
         <row r="99">
           <cell r="C99">
@@ -2433,7 +2433,13 @@
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="3"/>
+      <sheetData sheetId="3">
+        <row r="77">
+          <cell r="B77">
+            <v>8.1278569907775841E-5</v>
+          </cell>
+        </row>
+      </sheetData>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -2503,7 +2509,7 @@
       <sheetName val="LCI"/>
     </sheetNames>
     <sheetDataSet>
-      <sheetData sheetId="0"/>
+      <sheetData sheetId="0" refreshError="1"/>
       <sheetData sheetId="1">
         <row r="4">
           <cell r="C4">
@@ -4109,7 +4115,7 @@
         <v>494</v>
       </c>
       <c r="B51" s="114"/>
-      <c r="C51" s="115">
+      <c r="C51" s="112">
         <f>C5+C38-C44</f>
         <v>-267.29345925553793</v>
       </c>

--- a/LCA_techV3.xlsx
+++ b/LCA_techV3.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Users\hravoaha\Desktop\Thèse\Thèse 2023\Objectif 2\biowaste_optim\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E88FB3CC-E10D-4048-9F87-F50E1EC2C8D6}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E2B037C9-30B2-47A9-BA9C-9E72E51FE1D9}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="19200" windowHeight="6640" activeTab="11" xr2:uid="{D3821372-1969-4DD6-A628-04C5F8F02CF2}"/>
+    <workbookView minimized="1" xWindow="0" yWindow="0" windowWidth="19200" windowHeight="6640" firstSheet="17" activeTab="21" xr2:uid="{D3821372-1969-4DD6-A628-04C5F8F02CF2}"/>
   </bookViews>
   <sheets>
     <sheet name="LCIA_AD-f" sheetId="38" r:id="rId1"/>
@@ -2403,8 +2403,8 @@
       <sheetName val="Variables"/>
     </sheetNames>
     <sheetDataSet>
-      <sheetData sheetId="0" refreshError="1"/>
-      <sheetData sheetId="1" refreshError="1"/>
+      <sheetData sheetId="0"/>
+      <sheetData sheetId="1"/>
       <sheetData sheetId="2">
         <row r="99">
           <cell r="C99">
@@ -2433,13 +2433,7 @@
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="3">
-        <row r="77">
-          <cell r="B77">
-            <v>8.1278569907775841E-5</v>
-          </cell>
-        </row>
-      </sheetData>
+      <sheetData sheetId="3"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -2509,7 +2503,7 @@
       <sheetName val="LCI"/>
     </sheetNames>
     <sheetDataSet>
-      <sheetData sheetId="0" refreshError="1"/>
+      <sheetData sheetId="0"/>
       <sheetData sheetId="1">
         <row r="4">
           <cell r="C4">
